--- a/OZET_usa.xlsx
+++ b/OZET_usa.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %63.9 / Azalis %58.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %93.8 / Azalis %88.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %64.0 / Azalis %58.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %92.9 / Azalis %89.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.4 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=YOK</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %42.0 / Azalis %38.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %68.4 / Azalis %63.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.1 / Azalis %72.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %82.3 / Azalis %81.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %38.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %68.4 / Azalis %63.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.1 / Azalis %72.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %82.3 / Azalis %81.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %62.2 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %77.6 / Azalis %62.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.5 / Azalis %70.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.5 / Azalis %79.5 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %62.2 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %77.7 / Azalis %62.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.5 / Azalis %70.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.5 / Azalis %79.5 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.2 / Azalis %53.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %70.7 / Azalis %69.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.1 / Azalis %81.0 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %83.6 / Azalis %88.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
+          <t>NÖTR: PHL 1g: Artis %51.0 / Azalis %54.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %70.6 / Azalis %69.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.0 / Azalis %80.9 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %83.7 / Azalis %88.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %43.0 / Azalis %41.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %63.3 / Azalis %59.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %69.8 / Azalis %71.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.9 / Azalis %79.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %43.0 / Azalis %41.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %63.3 / Azalis %59.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %69.8 / Azalis %71.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.9 / Azalis %79.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %60.7 / Azalis %51.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.9 / Azalis %67.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.3 / Azalis %71.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.2 / Azalis %77.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %60.8 / Azalis %51.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.9 / Azalis %67.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.3 / Azalis %71.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.2 / Azalis %77.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %47.7 / Azalis %46.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.8 / Azalis %66.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.7 / Azalis %71.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %83.5 / Azalis %81.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %47.5 / Azalis %46.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.7 / Azalis %66.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.6 / Azalis %71.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %83.5 / Azalis %81.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %39.2 / Azalis %46.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %71.4 / Azalis %60.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %82.2 / Azalis %64.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %87.9 / Azalis %73.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %40.3 / Azalis %47.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %71.2 / Azalis %60.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %81.9 / Azalis %64.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %87.6 / Azalis %73.0 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %46.3 / Azalis %45.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %67.4 / Azalis %68.2 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.3 / Azalis %74.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %83.2 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %46.3 / Azalis %45.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %67.4 / Azalis %68.2 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.3 / Azalis %74.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %83.1 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %53.4 / Azalis %47.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.2 / Azalis %64.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.8 / Azalis %71.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %85.3 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %53.4 / Azalis %47.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.3 / Azalis %64.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.8 / Azalis %71.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %85.3 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %44.1 / Azalis %38.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %61.4 / Azalis %65.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %69.6 / Azalis %78.3 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %76.8 / Azalis %84.7 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %43.7 / Azalis %39.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.9 / Azalis %66.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %69.1 / Azalis %78.4 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %76.2 / Azalis %84.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %34.5 / Azalis %40.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %58.9 / Azalis %57.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %66.1 / Azalis %71.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %72.7 / Azalis %76.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %34.5 / Azalis %40.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %58.9 / Azalis %57.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %66.1 / Azalis %71.0 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %72.7 / Azalis %76.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %42.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %50.9 / Azalis %62.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %61.1 / Azalis %66.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %72.6 / Azalis %76.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %42.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %51.3 / Azalis %61.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %61.5 / Azalis %65.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %72.6 / Azalis %76.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %48.6 / Azalis %31.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %79.0 / Azalis %47.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %88.3 / Azalis %60.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %93.4 / Azalis %64.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %48.0 / Azalis %32.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.6 / Azalis %48.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.7 / Azalis %61.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %92.7 / Azalis %65.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %41.4 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.1 / Azalis %54.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %68.3 / Azalis %66.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %77.0 / Azalis %73.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %41.4 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.2 / Azalis %54.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %68.3 / Azalis %66.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %77.0 / Azalis %72.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %63.9 / Azalis %58.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %93.8 / Azalis %88.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %64.0 / Azalis %58.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %92.9 / Azalis %89.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.4 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=YOK</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %63.9 / Azalis %58.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %93.8 / Azalis %88.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %64.0 / Azalis %58.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %81.4 / Azalis %77.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %87.9 / Azalis %82.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %92.9 / Azalis %89.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %61.4 / Azalis %50.6 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %81.8 / Azalis %65.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.0 / Azalis %67.8 / AL 3 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %88.9 / Azalis %78.4 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=YOK</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %42.0 / Azalis %38.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %68.4 / Azalis %63.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.1 / Azalis %72.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %82.3 / Azalis %81.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %38.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %68.4 / Azalis %63.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.1 / Azalis %72.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %82.3 / Azalis %81.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %62.2 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %77.6 / Azalis %62.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.5 / Azalis %70.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.5 / Azalis %79.5 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %62.2 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %77.7 / Azalis %62.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.5 / Azalis %70.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.5 / Azalis %79.5 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.2 / Azalis %53.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %70.7 / Azalis %69.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.1 / Azalis %81.0 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %83.6 / Azalis %88.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
+          <t>NÖTR: PHL 1g: Artis %51.0 / Azalis %54.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %70.6 / Azalis %69.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.0 / Azalis %80.9 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %83.7 / Azalis %88.6 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %43.0 / Azalis %41.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %63.3 / Azalis %59.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %69.8 / Azalis %71.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.9 / Azalis %79.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %43.0 / Azalis %41.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %63.3 / Azalis %59.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %69.8 / Azalis %71.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.9 / Azalis %79.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %60.7 / Azalis %51.9 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.9 / Azalis %67.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.3 / Azalis %71.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.2 / Azalis %77.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %60.8 / Azalis %51.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.9 / Azalis %67.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %82.3 / Azalis %71.7 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.2 / Azalis %77.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %47.7 / Azalis %46.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.8 / Azalis %66.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.7 / Azalis %71.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %83.5 / Azalis %81.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %47.5 / Azalis %46.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.7 / Azalis %66.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.6 / Azalis %71.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %83.5 / Azalis %81.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %39.2 / Azalis %46.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %71.4 / Azalis %60.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %82.2 / Azalis %64.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %87.9 / Azalis %73.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %40.3 / Azalis %47.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %71.2 / Azalis %60.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %81.9 / Azalis %64.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %87.6 / Azalis %73.0 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %46.3 / Azalis %45.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %67.4 / Azalis %68.2 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.3 / Azalis %74.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %83.2 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %46.3 / Azalis %45.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %67.4 / Azalis %68.2 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.3 / Azalis %74.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %83.1 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %53.4 / Azalis %47.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.2 / Azalis %64.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.8 / Azalis %71.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %85.3 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %53.4 / Azalis %47.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %73.3 / Azalis %64.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %78.8 / Azalis %71.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %85.3 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %44.1 / Azalis %38.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %61.4 / Azalis %65.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %69.6 / Azalis %78.3 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %76.8 / Azalis %84.7 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %43.7 / Azalis %39.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.9 / Azalis %66.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %69.1 / Azalis %78.4 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %76.2 / Azalis %84.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %34.5 / Azalis %40.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %58.9 / Azalis %57.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %66.1 / Azalis %71.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %72.7 / Azalis %76.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %34.5 / Azalis %40.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %58.9 / Azalis %57.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %66.1 / Azalis %71.0 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %72.7 / Azalis %76.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %42.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %50.9 / Azalis %62.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %61.1 / Azalis %66.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %72.6 / Azalis %76.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %42.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %51.3 / Azalis %61.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %61.5 / Azalis %65.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %72.6 / Azalis %76.1 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %48.6 / Azalis %31.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %79.0 / Azalis %47.6 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %88.3 / Azalis %60.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %93.4 / Azalis %64.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %48.0 / Azalis %32.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.6 / Azalis %48.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %87.7 / Azalis %61.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %92.7 / Azalis %65.5 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %41.4 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.1 / Azalis %54.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %68.3 / Azalis %66.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %77.0 / Azalis %73.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %29.2 / Azalis %41.4 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.2 / Azalis %54.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %68.3 / Azalis %66.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %77.0 / Azalis %72.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">

--- a/OZET_usa.xlsx
+++ b/OZET_usa.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.7 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.8 / Azalis %80.0 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.8 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.6 / Azalis %79.9 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.6 / Azalis %47.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.9 / Azalis %58.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %70.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.1 / Azalis %48.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.3 / Azalis %58.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.2 / Azalis %71.0 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %43.8 / Azalis %49.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %67.2 / Azalis %71.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %77.2 / Azalis %74.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.6 / Azalis %79.1 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %44.4 / Azalis %49.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %68.4 / Azalis %70.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %76.9 / Azalis %74.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.3 / Azalis %78.8 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.1 / Azalis %83.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.4 / Azalis %83.3 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %40.7 / Azalis %46.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %62.6 / Azalis %71.4 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %72.7 / Azalis %77.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %80.7 / Azalis %86.7 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
+          <t>NÖTR: PHL 1g: Artis %40.7 / Azalis %46.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %62.6 / Azalis %71.4 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %73.0 / Azalis %76.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %80.9 / Azalis %86.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.8 / Azalis %31.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %71.1 / Azalis %52.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.9 / Azalis %67.8 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.6 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %52.1 / Azalis %31.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.9 / Azalis %52.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.8 / Azalis %67.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.6 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %57.3 / Azalis %44.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %76.0 / Azalis %62.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.5 / Azalis %70.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %85.9 / Azalis %76.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %57.3 / Azalis %43.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %75.9 / Azalis %62.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.4 / Azalis %71.0 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %85.9 / Azalis %76.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %46.9 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %66.6 / Azalis %62.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %73.6 / Azalis %69.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %79.0 / Azalis %79.7 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %46.9 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %66.6 / Azalis %62.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %73.6 / Azalis %69.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %79.0 / Azalis %79.7 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %61.1 / Azalis %61.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %75.0 / Azalis %75.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %79.0 / Azalis %78.8 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %84.5 / Azalis %84.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %61.1 / Azalis %61.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %75.3 / Azalis %76.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %79.2 / Azalis %78.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %84.5 / Azalis %84.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.7 / Azalis %45.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %69.9 / Azalis %67.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %73.9 / Azalis %72.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.1 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %51.7 / Azalis %45.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %69.9 / Azalis %67.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %73.9 / Azalis %72.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.1 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=^NDX | Karar=SAT_ADAYI | AL basari=56.25 n=48 | SAT basari=nan n=1</t>
+          <t>OLUMSUZ / RİSK: Endeks=^NDX | Karar=SAT_ADAYI | AL basari=55.10204081632653 n=49 | SAT basari=nan n=1</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %50.5 / Azalis %52.8 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %71.7 / Azalis %74.4 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.6 / Azalis %84.0 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %84.8 / Azalis %90.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %50.8 / Azalis %53.1 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %71.8 / Azalis %74.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.7 / Azalis %84.1 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %84.8 / Azalis %90.7 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %58.0 / Azalis %43.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.5 / Azalis %58.7 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %84.4 / Azalis %62.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %86.0 / Azalis %76.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %58.1 / Azalis %43.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.5 / Azalis %58.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %84.4 / Azalis %62.8 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %86.1 / Azalis %76.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %59.5 / Azalis %61.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %80.5 / Azalis %76.5 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %86.6 / Azalis %81.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %91.0 / Azalis %86.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %59.5 / Azalis %61.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %80.6 / Azalis %76.5 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %86.6 / Azalis %81.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %91.0 / Azalis %86.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %34.7 / Azalis %45.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %67.6 / Azalis %66.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.0 / Azalis %73.1 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %87.1 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %35.3 / Azalis %45.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %67.9 / Azalis %67.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.2 / Azalis %73.4 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %87.1 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+10.5% → -9.8% | M Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+3.9% → -6.3% | S Now=Now +8.1%, L -1.8%, H +8.1%, UD; Path=-5.1% → +18.7% | WMA200=+11.8%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+10.5% → -9.8% | M Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+3.9% → -6.3% | S Now=Now +8.1%, L -1.8%, H +8.1%, UD; Path=-5.1% → +18.7% | WMA200=+11.7%, DOWN</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %50.0 / Azalis %45.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.5 / Azalis %67.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.7 / Azalis %74.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.8 / Azalis %83.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %48.5 / Azalis %43.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.2 / Azalis %66.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.1 / Azalis %75.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.8 / Azalis %82.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %41.3 / Azalis %42.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.6 / Azalis %57.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %72.0 / Azalis %65.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %82.3 / Azalis %77.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %42.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.6 / Azalis %57.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %72.0 / Azalis %65.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %82.3 / Azalis %77.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.7 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.8 / Azalis %80.0 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.8 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.6 / Azalis %79.9 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.6 / Azalis %47.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.9 / Azalis %58.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %70.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.1 / Azalis %48.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.3 / Azalis %58.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.2 / Azalis %71.0 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %43.8 / Azalis %49.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %67.2 / Azalis %71.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %77.2 / Azalis %74.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.6 / Azalis %79.1 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %44.4 / Azalis %49.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %68.4 / Azalis %70.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %76.9 / Azalis %74.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.3 / Azalis %78.8 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.1 / Azalis %83.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.4 / Azalis %83.3 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %49.6 / Azalis %40.3 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.1 / Azalis %59.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %75.4 / Azalis %70.1 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %84.2 / Azalis %76.7 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.7 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.8 / Azalis %80.0 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %54.7 / Azalis %57.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %75.8 / Azalis %71.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 5g: Artis %81.6 / Azalis %79.9 / AL 2 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %86.3 / Azalis %85.2 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.6 / Azalis %47.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.9 / Azalis %58.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.8 / Azalis %70.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %31.9 / Azalis %32.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %65.1 / Azalis %48.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %74.3 / Azalis %58.9 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %81.2 / Azalis %71.0 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %43.8 / Azalis %49.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %67.2 / Azalis %71.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %77.2 / Azalis %74.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.6 / Azalis %79.1 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %44.4 / Azalis %49.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 3g: Artis %68.4 / Azalis %70.5 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %76.9 / Azalis %74.3 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %89.3 / Azalis %78.8 / AL 3 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.1 / Azalis %83.1 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %39.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %60.0 / Azalis %67.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %69.1 / Azalis %75.0 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %79.4 / Azalis %83.3 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=N</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %40.7 / Azalis %46.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %62.6 / Azalis %71.4 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %72.7 / Azalis %77.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %80.7 / Azalis %86.7 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
+          <t>NÖTR: PHL 1g: Artis %40.7 / Azalis %46.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %62.6 / Azalis %71.4 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 5g: Artis %73.0 / Azalis %76.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %80.9 / Azalis %86.8 / AL 0 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor -4</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.8 / Azalis %31.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %71.1 / Azalis %52.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.9 / Azalis %67.8 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.6 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %52.1 / Azalis %31.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %70.9 / Azalis %52.1 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.8 / Azalis %67.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %86.6 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %57.3 / Azalis %44.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %76.0 / Azalis %62.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.5 / Azalis %70.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %85.9 / Azalis %76.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %57.3 / Azalis %43.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %75.9 / Azalis %62.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %78.4 / Azalis %71.0 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %85.9 / Azalis %76.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -16345,7 +16345,7 @@
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %46.9 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %66.6 / Azalis %62.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %73.6 / Azalis %69.8 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %79.0 / Azalis %79.7 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %46.9 / Azalis %43.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %66.6 / Azalis %62.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %73.6 / Azalis %69.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %79.0 / Azalis %79.7 / AL 0 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %61.1 / Azalis %61.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %75.0 / Azalis %75.8 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %79.0 / Azalis %78.8 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %84.5 / Azalis %84.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %61.1 / Azalis %61.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %75.3 / Azalis %76.0 / AL 1 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %79.2 / Azalis %78.9 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %84.5 / Azalis %84.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %51.7 / Azalis %45.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %69.9 / Azalis %67.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %73.9 / Azalis %72.7 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.1 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %51.7 / Azalis %45.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %69.9 / Azalis %67.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %73.9 / Azalis %72.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.1 / Azalis %78.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -17277,12 +17277,12 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=N</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: Endeks=^NDX | Karar=SAT_ADAYI | AL basari=56.25 n=48 | SAT basari=nan n=1</t>
+          <t>OLUMSUZ / RİSK: Endeks=^NDX | Karar=SAT_ADAYI | AL basari=55.10204081632653 n=49 | SAT basari=nan n=1</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %50.5 / Azalis %52.8 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %71.7 / Azalis %74.4 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.6 / Azalis %84.0 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %84.8 / Azalis %90.6 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
+          <t>NÖTR: PHL 1g: Artis %50.8 / Azalis %53.1 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 3g: Artis %71.8 / Azalis %74.6 / AL 2 / SAT 2 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %76.7 / Azalis %84.1 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2 | PHL 10g: Artis %84.8 / Azalis %90.7 / AL 2 / SAT 3 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=D</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=U; gun-kosullu: 3g=N / 4g=U</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=U / 4g=YOK</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=N; gun-kosullu: 3g=D / 4g=N</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %58.0 / Azalis %43.6 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.5 / Azalis %58.7 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %84.4 / Azalis %62.9 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %86.0 / Azalis %76.2 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
+          <t>NÖTR: PHL 1g: Artis %58.1 / Azalis %43.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 3g: Artis %78.5 / Azalis %58.4 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 5g: Artis %84.4 / Azalis %62.8 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %86.1 / Azalis %76.3 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
+          <t>OLUMLU: BIS genel kapanis: 3g=U / 4g=U; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %59.5 / Azalis %61.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %80.5 / Azalis %76.5 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %86.6 / Azalis %81.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %91.0 / Azalis %86.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %59.5 / Azalis %61.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %80.6 / Azalis %76.5 / AL 1 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %86.6 / Azalis %81.6 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %91.0 / Azalis %86.3 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=D / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=D / 4g=U; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>OLUMSUZ / RİSK: BIS genel kapanis: 3g=D / 4g=D; gun-kosullu: 3g=D / 4g=D</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %34.7 / Azalis %45.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %67.6 / Azalis %66.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.0 / Azalis %73.1 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %87.1 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %35.3 / Azalis %45.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor -4 | PHL 3g: Artis %67.9 / Azalis %67.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %80.2 / Azalis %73.4 / AL 1 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 10g: Artis %87.1 / Azalis %74.6 / AL 2 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+10.5% → -9.8% | M Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+3.9% → -6.3% | S Now=Now +8.1%, L -1.8%, H +8.1%, UD; Path=-5.1% → +18.7% | WMA200=+11.8%, DOWN</t>
+          <t>OLUMLU: Action=LONG_WATCH | Trade_Action=LONG_WATCH | Önerilen=HAYIR | Öneren sistem=0 | Q Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+10.5% → -9.8% | M Now=Now +0.0%, L -0.0%, H +0.0%, DU; Path=+3.9% → -6.3% | S Now=Now +8.1%, L -1.8%, H +8.1%, UD; Path=-5.1% → +18.7% | WMA200=+11.7%, DOWN</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=N</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %50.0 / Azalis %45.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.5 / Azalis %67.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.7 / Azalis %74.9 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %81.8 / Azalis %83.5 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor 0</t>
+          <t>NÖTR: PHL 1g: Artis %48.5 / Azalis %43.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %65.2 / Azalis %66.2 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 5g: Artis %75.1 / Azalis %75.5 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 10g: Artis %80.8 / Azalis %82.9 / AL 0 / SAT 1 / Karne olculmedi / Endeksi gecme - / Skor -2</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=U / 4g=D</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=U</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=D / 4g=D</t>
+          <t>NÖTR: BIS genel kapanis: 3g=N / 4g=N; gun-kosullu: 3g=N / 4g=N</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: PHL 1g: Artis %41.3 / Azalis %42.7 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.6 / Azalis %57.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %72.0 / Azalis %65.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %82.3 / Azalis %77.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
+          <t>NÖTR: PHL 1g: Artis %41.8 / Azalis %42.3 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 0 | PHL 3g: Artis %66.6 / Azalis %57.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2 | PHL 5g: Artis %72.0 / Azalis %65.0 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 4 | PHL 10g: Artis %82.3 / Azalis %77.1 / AL 0 / SAT 0 / Karne olculmedi / Endeksi gecme - / Skor 2</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=N / 4g=N</t>
+          <t>NÖTR: BIS genel kapanis: 3g=U / 4g=D; gun-kosullu: 3g=U / 4g=U</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
